--- a/sources/ling_step3.xlsx
+++ b/sources/ling_step3.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -459,12 +459,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">

--- a/sources/ling_step3.xlsx
+++ b/sources/ling_step3.xlsx
@@ -836,6 +836,11 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
@@ -873,6 +878,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
@@ -910,6 +920,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
@@ -945,6 +960,11 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -7300,6 +7320,11 @@
           <t>mhhmmMLLmm</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
@@ -7325,6 +7350,11 @@
       <c r="I150" t="inlineStr">
         <is>
           <t>mhhLLmmllmm</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
